--- a/regression_deneme/regression_with_nn/Mürselpaşa Bulvarı_weekly_true_and_predicted_test.xlsx
+++ b/regression_deneme/regression_with_nn/Mürselpaşa Bulvarı_weekly_true_and_predicted_test.xlsx
@@ -461,7 +461,7 @@
         <v>6</v>
       </c>
       <c r="D2" t="n">
-        <v>3.675908703152043</v>
+        <v>2.909907467882422</v>
       </c>
     </row>
     <row r="3">
@@ -475,7 +475,7 @@
         <v>17</v>
       </c>
       <c r="D3" t="n">
-        <v>12.48205303821337</v>
+        <v>16.08400437154739</v>
       </c>
     </row>
     <row r="4">
@@ -489,7 +489,7 @@
         <v>30</v>
       </c>
       <c r="D4" t="n">
-        <v>21.43292256237012</v>
+        <v>20.4343654593415</v>
       </c>
     </row>
     <row r="5">
@@ -503,7 +503,7 @@
         <v>15</v>
       </c>
       <c r="D5" t="n">
-        <v>18.95582928043034</v>
+        <v>17.63588625711897</v>
       </c>
     </row>
     <row r="6">
@@ -517,7 +517,7 @@
         <v>8</v>
       </c>
       <c r="D6" t="n">
-        <v>14.07139124294931</v>
+        <v>17.02275928674725</v>
       </c>
     </row>
     <row r="7">
@@ -531,7 +531,7 @@
         <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>12.25224448902165</v>
+        <v>11.18207583374701</v>
       </c>
     </row>
     <row r="8">
@@ -545,7 +545,7 @@
         <v>14</v>
       </c>
       <c r="D8" t="n">
-        <v>13.87779167006502</v>
+        <v>10.38425424281604</v>
       </c>
     </row>
     <row r="9">
@@ -559,7 +559,7 @@
         <v>10</v>
       </c>
       <c r="D9" t="n">
-        <v>14.94588099553865</v>
+        <v>11.19664834699264</v>
       </c>
     </row>
     <row r="10">
@@ -573,7 +573,7 @@
         <v>14</v>
       </c>
       <c r="D10" t="n">
-        <v>12.33375825050006</v>
+        <v>12.80903195739837</v>
       </c>
     </row>
     <row r="11">
@@ -587,7 +587,7 @@
         <v>7</v>
       </c>
       <c r="D11" t="n">
-        <v>8.235685411704752</v>
+        <v>9.645461835401813</v>
       </c>
     </row>
     <row r="12">
@@ -601,7 +601,7 @@
         <v>9</v>
       </c>
       <c r="D12" t="n">
-        <v>10.00003835480935</v>
+        <v>10.07104808651077</v>
       </c>
     </row>
     <row r="13">
@@ -615,7 +615,7 @@
         <v>15</v>
       </c>
       <c r="D13" t="n">
-        <v>12.46809024671736</v>
+        <v>11.09070342144361</v>
       </c>
     </row>
     <row r="14">
@@ -629,7 +629,7 @@
         <v>14</v>
       </c>
       <c r="D14" t="n">
-        <v>12.64076586308316</v>
+        <v>12.28003595556026</v>
       </c>
     </row>
     <row r="15">
@@ -643,7 +643,7 @@
         <v>6</v>
       </c>
       <c r="D15" t="n">
-        <v>9.289310171707466</v>
+        <v>10.96056544885008</v>
       </c>
     </row>
     <row r="16">
@@ -657,7 +657,7 @@
         <v>15</v>
       </c>
       <c r="D16" t="n">
-        <v>14.28288440516883</v>
+        <v>11.98620679898637</v>
       </c>
     </row>
     <row r="17">
@@ -671,7 +671,7 @@
         <v>10</v>
       </c>
       <c r="D17" t="n">
-        <v>10.11321618226349</v>
+        <v>11.72411546471643</v>
       </c>
     </row>
     <row r="18">
@@ -685,7 +685,7 @@
         <v>20</v>
       </c>
       <c r="D18" t="n">
-        <v>11.60871312814789</v>
+        <v>11.82419188078504</v>
       </c>
     </row>
     <row r="19">
@@ -699,7 +699,7 @@
         <v>8</v>
       </c>
       <c r="D19" t="n">
-        <v>11.4544861523618</v>
+        <v>12.65478776780046</v>
       </c>
     </row>
     <row r="20">
@@ -713,7 +713,7 @@
         <v>6</v>
       </c>
       <c r="D20" t="n">
-        <v>8.830042482941087</v>
+        <v>11.95039628026134</v>
       </c>
     </row>
     <row r="21">
@@ -727,7 +727,7 @@
         <v>11</v>
       </c>
       <c r="D21" t="n">
-        <v>15.947133981199</v>
+        <v>9.257307300045134</v>
       </c>
     </row>
     <row r="22">
@@ -741,7 +741,7 @@
         <v>13</v>
       </c>
       <c r="D22" t="n">
-        <v>11.67918940552482</v>
+        <v>10.44104885753071</v>
       </c>
     </row>
     <row r="23">
@@ -755,7 +755,7 @@
         <v>10</v>
       </c>
       <c r="D23" t="n">
-        <v>10.46675418025485</v>
+        <v>10.52931440988895</v>
       </c>
     </row>
     <row r="24">
@@ -769,7 +769,7 @@
         <v>8</v>
       </c>
       <c r="D24" t="n">
-        <v>9.099246359094064</v>
+        <v>10.21717578357585</v>
       </c>
     </row>
     <row r="25">
@@ -783,7 +783,7 @@
         <v>10</v>
       </c>
       <c r="D25" t="n">
-        <v>9.783895235949098</v>
+        <v>10.81678348095233</v>
       </c>
     </row>
     <row r="26">
@@ -797,7 +797,7 @@
         <v>10</v>
       </c>
       <c r="D26" t="n">
-        <v>8.813472950568835</v>
+        <v>9.060934298568728</v>
       </c>
     </row>
     <row r="27">
@@ -811,7 +811,7 @@
         <v>8</v>
       </c>
       <c r="D27" t="n">
-        <v>8.187704102213502</v>
+        <v>10.42117006699047</v>
       </c>
     </row>
     <row r="28">
@@ -825,7 +825,7 @@
         <v>9</v>
       </c>
       <c r="D28" t="n">
-        <v>10.46362736253344</v>
+        <v>10.27785588780602</v>
       </c>
     </row>
     <row r="29">
@@ -839,7 +839,7 @@
         <v>12</v>
       </c>
       <c r="D29" t="n">
-        <v>11.16473115794367</v>
+        <v>9.099030240069004</v>
       </c>
     </row>
     <row r="30">
@@ -853,7 +853,7 @@
         <v>9</v>
       </c>
       <c r="D30" t="n">
-        <v>9.676788755942567</v>
+        <v>10.69995925440739</v>
       </c>
     </row>
     <row r="31">
@@ -867,7 +867,7 @@
         <v>11</v>
       </c>
       <c r="D31" t="n">
-        <v>9.109239853424457</v>
+        <v>9.47311144802095</v>
       </c>
     </row>
     <row r="32">
@@ -881,7 +881,7 @@
         <v>12</v>
       </c>
       <c r="D32" t="n">
-        <v>12.0687977793331</v>
+        <v>12.03016174156572</v>
       </c>
     </row>
   </sheetData>
